--- a/data/raw/results-survey739381.xlsx
+++ b/data/raw/results-survey739381.xlsx
@@ -107,7 +107,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:EG171"/>
+  <dimension ref="A1:EG186"/>
   <cols>
     <col collapsed="false" hidden="false" max="1024" min="1" style="0" customWidth="false" width="11.5"/>
   </cols>
@@ -50209,6 +50209,4411 @@
       <c r="EF171" s="0"/>
       <c r="EG171" s="0"/>
     </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="172">
+      <c r="A172" s="0" t="n">
+        <v>229</v>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D172" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E172" s="0" t="n">
+        <v>395569935</v>
+      </c>
+      <c r="F172" s="0" t="inlineStr">
+        <is>
+          <t>20–30</t>
+        </is>
+      </c>
+      <c r="G172" s="0"/>
+      <c r="H172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="L172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N172" s="0"/>
+      <c r="O172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P172" s="0"/>
+      <c r="Q172" s="0"/>
+      <c r="R172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W172" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X172" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA172" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB172" s="0"/>
+      <c r="AC172" s="0"/>
+      <c r="AD172" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="AE172" s="0"/>
+      <c r="AF172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB172" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC172" s="0"/>
+      <c r="BD172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE172" s="0"/>
+      <c r="BF172" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH172" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI172" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK172" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL172" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM172" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN172" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO172" s="0"/>
+      <c r="BP172" s="0"/>
+      <c r="BQ172" s="0" t="n">
+        <v>675.14</v>
+      </c>
+      <c r="BR172" s="0"/>
+      <c r="BS172" s="0"/>
+      <c r="BT172" s="0" t="n">
+        <v>277.32</v>
+      </c>
+      <c r="BU172" s="0"/>
+      <c r="BV172" s="0" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="BW172" s="0"/>
+      <c r="BX172" s="0"/>
+      <c r="BY172" s="0"/>
+      <c r="BZ172" s="0"/>
+      <c r="CA172" s="0"/>
+      <c r="CB172" s="0" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="CC172" s="0"/>
+      <c r="CD172" s="0"/>
+      <c r="CE172" s="0"/>
+      <c r="CF172" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="CG172" s="0"/>
+      <c r="CH172" s="0" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="CI172" s="0"/>
+      <c r="CJ172" s="0"/>
+      <c r="CK172" s="0"/>
+      <c r="CL172" s="0"/>
+      <c r="CM172" s="0"/>
+      <c r="CN172" s="0" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="CO172" s="0"/>
+      <c r="CP172" s="0"/>
+      <c r="CQ172" s="0"/>
+      <c r="CR172" s="0"/>
+      <c r="CS172" s="0" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="CT172" s="0"/>
+      <c r="CU172" s="0"/>
+      <c r="CV172" s="0" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="CW172" s="0"/>
+      <c r="CX172" s="0" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="CY172" s="0"/>
+      <c r="CZ172" s="0"/>
+      <c r="DA172" s="0" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="DB172" s="0"/>
+      <c r="DC172" s="0" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="DD172" s="0"/>
+      <c r="DE172" s="0"/>
+      <c r="DF172" s="0"/>
+      <c r="DG172" s="0"/>
+      <c r="DH172" s="0" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="DI172" s="0"/>
+      <c r="DJ172" s="0"/>
+      <c r="DK172" s="0" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="DL172" s="0"/>
+      <c r="DM172" s="0"/>
+      <c r="DN172" s="0"/>
+      <c r="DO172" s="0" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="DP172" s="0"/>
+      <c r="DQ172" s="0" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="DR172" s="0"/>
+      <c r="DS172" s="0"/>
+      <c r="DT172" s="0"/>
+      <c r="DU172" s="0" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="DV172" s="0"/>
+      <c r="DW172" s="0"/>
+      <c r="DX172" s="0"/>
+      <c r="DY172" s="0"/>
+      <c r="DZ172" s="0"/>
+      <c r="EA172" s="0"/>
+      <c r="EB172" s="0"/>
+      <c r="EC172" s="0"/>
+      <c r="ED172" s="0" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="EE172" s="0"/>
+      <c r="EF172" s="0"/>
+      <c r="EG172" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="173">
+      <c r="A173" s="0" t="n">
+        <v>230</v>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E173" s="0" t="n">
+        <v>137423609</v>
+      </c>
+      <c r="F173" s="0" t="inlineStr">
+        <is>
+          <t>20–30</t>
+        </is>
+      </c>
+      <c r="G173" s="0"/>
+      <c r="H173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M173" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="N173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="O173" s="0"/>
+      <c r="P173" s="0"/>
+      <c r="Q173" s="0"/>
+      <c r="R173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="S173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V173" s="0"/>
+      <c r="W173" s="0"/>
+      <c r="X173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y173" s="0"/>
+      <c r="Z173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB173" s="0"/>
+      <c r="AC173" s="0"/>
+      <c r="AD173" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE173" s="0"/>
+      <c r="AF173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH173" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ173" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK173" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB173" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC173" s="0"/>
+      <c r="BD173" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF173" s="0"/>
+      <c r="BG173" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH173" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI173" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK173" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM173" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN173" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO173" s="0"/>
+      <c r="BP173" s="0"/>
+      <c r="BQ173" s="0" t="n">
+        <v>664.59</v>
+      </c>
+      <c r="BR173" s="0"/>
+      <c r="BS173" s="0"/>
+      <c r="BT173" s="0" t="n">
+        <v>201.09</v>
+      </c>
+      <c r="BU173" s="0"/>
+      <c r="BV173" s="0" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="BW173" s="0"/>
+      <c r="BX173" s="0"/>
+      <c r="BY173" s="0"/>
+      <c r="BZ173" s="0"/>
+      <c r="CA173" s="0"/>
+      <c r="CB173" s="0" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="CC173" s="0"/>
+      <c r="CD173" s="0"/>
+      <c r="CE173" s="0"/>
+      <c r="CF173" s="0" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="CG173" s="0"/>
+      <c r="CH173" s="0" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="CI173" s="0"/>
+      <c r="CJ173" s="0"/>
+      <c r="CK173" s="0"/>
+      <c r="CL173" s="0"/>
+      <c r="CM173" s="0"/>
+      <c r="CN173" s="0" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="CO173" s="0"/>
+      <c r="CP173" s="0"/>
+      <c r="CQ173" s="0"/>
+      <c r="CR173" s="0"/>
+      <c r="CS173" s="0" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="CT173" s="0"/>
+      <c r="CU173" s="0"/>
+      <c r="CV173" s="0" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="CW173" s="0"/>
+      <c r="CX173" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="CY173" s="0"/>
+      <c r="CZ173" s="0"/>
+      <c r="DA173" s="0" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="DB173" s="0"/>
+      <c r="DC173" s="0" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="DD173" s="0"/>
+      <c r="DE173" s="0"/>
+      <c r="DF173" s="0"/>
+      <c r="DG173" s="0"/>
+      <c r="DH173" s="0" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="DI173" s="0"/>
+      <c r="DJ173" s="0"/>
+      <c r="DK173" s="0" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="DL173" s="0"/>
+      <c r="DM173" s="0"/>
+      <c r="DN173" s="0"/>
+      <c r="DO173" s="0" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="DP173" s="0"/>
+      <c r="DQ173" s="0" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="DR173" s="0"/>
+      <c r="DS173" s="0"/>
+      <c r="DT173" s="0"/>
+      <c r="DU173" s="0" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="DV173" s="0"/>
+      <c r="DW173" s="0"/>
+      <c r="DX173" s="0"/>
+      <c r="DY173" s="0"/>
+      <c r="DZ173" s="0"/>
+      <c r="EA173" s="0"/>
+      <c r="EB173" s="0"/>
+      <c r="EC173" s="0"/>
+      <c r="ED173" s="0" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="EE173" s="0"/>
+      <c r="EF173" s="0"/>
+      <c r="EG173" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="174">
+      <c r="A174" s="0" t="n">
+        <v>231</v>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E174" s="0" t="n">
+        <v>668432532</v>
+      </c>
+      <c r="F174" s="0" t="inlineStr">
+        <is>
+          <t>10–15</t>
+        </is>
+      </c>
+      <c r="G174" s="0"/>
+      <c r="H174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I174" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="N174" s="0"/>
+      <c r="O174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P174" s="0"/>
+      <c r="Q174" s="0"/>
+      <c r="R174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V174" s="0"/>
+      <c r="W174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="X174" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA174" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB174" s="0"/>
+      <c r="AC174" s="0"/>
+      <c r="AD174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE174" s="0"/>
+      <c r="AF174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB174" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC174" s="0"/>
+      <c r="BD174" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE174" s="0"/>
+      <c r="BF174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK174" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL174" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM174" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN174" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO174" s="0"/>
+      <c r="BP174" s="0"/>
+      <c r="BQ174" s="0" t="n">
+        <v>1073.63</v>
+      </c>
+      <c r="BR174" s="0"/>
+      <c r="BS174" s="0"/>
+      <c r="BT174" s="0" t="n">
+        <v>559.36</v>
+      </c>
+      <c r="BU174" s="0"/>
+      <c r="BV174" s="0" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="BW174" s="0"/>
+      <c r="BX174" s="0"/>
+      <c r="BY174" s="0"/>
+      <c r="BZ174" s="0"/>
+      <c r="CA174" s="0"/>
+      <c r="CB174" s="0" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="CC174" s="0"/>
+      <c r="CD174" s="0"/>
+      <c r="CE174" s="0"/>
+      <c r="CF174" s="0" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="CG174" s="0"/>
+      <c r="CH174" s="0" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="CI174" s="0"/>
+      <c r="CJ174" s="0"/>
+      <c r="CK174" s="0"/>
+      <c r="CL174" s="0"/>
+      <c r="CM174" s="0"/>
+      <c r="CN174" s="0" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="CO174" s="0"/>
+      <c r="CP174" s="0"/>
+      <c r="CQ174" s="0"/>
+      <c r="CR174" s="0"/>
+      <c r="CS174" s="0" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="CT174" s="0"/>
+      <c r="CU174" s="0"/>
+      <c r="CV174" s="0" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="CW174" s="0"/>
+      <c r="CX174" s="0" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="CY174" s="0"/>
+      <c r="CZ174" s="0"/>
+      <c r="DA174" s="0" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="DB174" s="0"/>
+      <c r="DC174" s="0" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="DD174" s="0"/>
+      <c r="DE174" s="0"/>
+      <c r="DF174" s="0"/>
+      <c r="DG174" s="0"/>
+      <c r="DH174" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="DI174" s="0"/>
+      <c r="DJ174" s="0"/>
+      <c r="DK174" s="0" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="DL174" s="0"/>
+      <c r="DM174" s="0"/>
+      <c r="DN174" s="0"/>
+      <c r="DO174" s="0" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="DP174" s="0"/>
+      <c r="DQ174" s="0" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="DR174" s="0"/>
+      <c r="DS174" s="0"/>
+      <c r="DT174" s="0"/>
+      <c r="DU174" s="0" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="DV174" s="0"/>
+      <c r="DW174" s="0"/>
+      <c r="DX174" s="0"/>
+      <c r="DY174" s="0"/>
+      <c r="DZ174" s="0"/>
+      <c r="EA174" s="0"/>
+      <c r="EB174" s="0"/>
+      <c r="EC174" s="0"/>
+      <c r="ED174" s="0" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="EE174" s="0"/>
+      <c r="EF174" s="0"/>
+      <c r="EG174" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="175">
+      <c r="A175" s="0" t="n">
+        <v>233</v>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E175" s="0" t="n">
+        <v>1358510776</v>
+      </c>
+      <c r="F175" s="0" t="inlineStr">
+        <is>
+          <t>3–5</t>
+        </is>
+      </c>
+      <c r="G175" s="0"/>
+      <c r="H175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="O175" s="0"/>
+      <c r="P175" s="0"/>
+      <c r="Q175" s="0"/>
+      <c r="R175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB175" s="0"/>
+      <c r="AC175" s="0"/>
+      <c r="AD175" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE175" s="0"/>
+      <c r="AF175" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH175" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI175" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK175" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB175" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC175" s="0"/>
+      <c r="BD175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF175" s="0"/>
+      <c r="BG175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH175" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI175" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ175" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK175" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM175" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN175" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO175" s="0"/>
+      <c r="BP175" s="0"/>
+      <c r="BQ175" s="0" t="n">
+        <v>859.7</v>
+      </c>
+      <c r="BR175" s="0"/>
+      <c r="BS175" s="0"/>
+      <c r="BT175" s="0" t="n">
+        <v>199.37</v>
+      </c>
+      <c r="BU175" s="0"/>
+      <c r="BV175" s="0" t="n">
+        <v>32.11</v>
+      </c>
+      <c r="BW175" s="0"/>
+      <c r="BX175" s="0"/>
+      <c r="BY175" s="0"/>
+      <c r="BZ175" s="0"/>
+      <c r="CA175" s="0"/>
+      <c r="CB175" s="0" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="CC175" s="0"/>
+      <c r="CD175" s="0"/>
+      <c r="CE175" s="0"/>
+      <c r="CF175" s="0" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="CG175" s="0"/>
+      <c r="CH175" s="0" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="CI175" s="0"/>
+      <c r="CJ175" s="0"/>
+      <c r="CK175" s="0"/>
+      <c r="CL175" s="0"/>
+      <c r="CM175" s="0"/>
+      <c r="CN175" s="0" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="CO175" s="0"/>
+      <c r="CP175" s="0"/>
+      <c r="CQ175" s="0"/>
+      <c r="CR175" s="0"/>
+      <c r="CS175" s="0" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="CT175" s="0"/>
+      <c r="CU175" s="0"/>
+      <c r="CV175" s="0" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="CW175" s="0"/>
+      <c r="CX175" s="0" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="CY175" s="0"/>
+      <c r="CZ175" s="0"/>
+      <c r="DA175" s="0" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="DB175" s="0"/>
+      <c r="DC175" s="0" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="DD175" s="0"/>
+      <c r="DE175" s="0"/>
+      <c r="DF175" s="0"/>
+      <c r="DG175" s="0"/>
+      <c r="DH175" s="0" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="DI175" s="0"/>
+      <c r="DJ175" s="0"/>
+      <c r="DK175" s="0" t="n">
+        <v>94.91</v>
+      </c>
+      <c r="DL175" s="0"/>
+      <c r="DM175" s="0"/>
+      <c r="DN175" s="0"/>
+      <c r="DO175" s="0" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="DP175" s="0"/>
+      <c r="DQ175" s="0" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="DR175" s="0"/>
+      <c r="DS175" s="0"/>
+      <c r="DT175" s="0"/>
+      <c r="DU175" s="0" t="n">
+        <v>83.08</v>
+      </c>
+      <c r="DV175" s="0"/>
+      <c r="DW175" s="0"/>
+      <c r="DX175" s="0"/>
+      <c r="DY175" s="0"/>
+      <c r="DZ175" s="0"/>
+      <c r="EA175" s="0"/>
+      <c r="EB175" s="0"/>
+      <c r="EC175" s="0"/>
+      <c r="ED175" s="0" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="EE175" s="0"/>
+      <c r="EF175" s="0"/>
+      <c r="EG175" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="176">
+      <c r="A176" s="0" t="n">
+        <v>235</v>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E176" s="0" t="n">
+        <v>1914037626</v>
+      </c>
+      <c r="F176" s="0" t="inlineStr">
+        <is>
+          <t>20–30</t>
+        </is>
+      </c>
+      <c r="G176" s="0"/>
+      <c r="H176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N176" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="O176" s="0"/>
+      <c r="P176" s="0"/>
+      <c r="Q176" s="0"/>
+      <c r="R176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W176" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="X176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y176" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB176" s="0"/>
+      <c r="AC176" s="0"/>
+      <c r="AD176" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE176" s="0"/>
+      <c r="AF176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG176" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI176" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK176" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL176" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC176" s="0"/>
+      <c r="BD176" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE176" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF176" s="0"/>
+      <c r="BG176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH176" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI176" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ176" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK176" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM176" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO176" s="0"/>
+      <c r="BP176" s="0"/>
+      <c r="BQ176" s="0" t="n">
+        <v>523.68</v>
+      </c>
+      <c r="BR176" s="0"/>
+      <c r="BS176" s="0"/>
+      <c r="BT176" s="0" t="n">
+        <v>201.11</v>
+      </c>
+      <c r="BU176" s="0"/>
+      <c r="BV176" s="0" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="BW176" s="0"/>
+      <c r="BX176" s="0"/>
+      <c r="BY176" s="0"/>
+      <c r="BZ176" s="0"/>
+      <c r="CA176" s="0"/>
+      <c r="CB176" s="0" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="CC176" s="0"/>
+      <c r="CD176" s="0"/>
+      <c r="CE176" s="0"/>
+      <c r="CF176" s="0" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="CG176" s="0"/>
+      <c r="CH176" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="CI176" s="0"/>
+      <c r="CJ176" s="0"/>
+      <c r="CK176" s="0"/>
+      <c r="CL176" s="0"/>
+      <c r="CM176" s="0"/>
+      <c r="CN176" s="0" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="CO176" s="0"/>
+      <c r="CP176" s="0"/>
+      <c r="CQ176" s="0"/>
+      <c r="CR176" s="0"/>
+      <c r="CS176" s="0" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="CT176" s="0"/>
+      <c r="CU176" s="0"/>
+      <c r="CV176" s="0" t="n">
+        <v>8.37</v>
+      </c>
+      <c r="CW176" s="0"/>
+      <c r="CX176" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="CY176" s="0"/>
+      <c r="CZ176" s="0"/>
+      <c r="DA176" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="DB176" s="0"/>
+      <c r="DC176" s="0" t="n">
+        <v>24.69</v>
+      </c>
+      <c r="DD176" s="0"/>
+      <c r="DE176" s="0"/>
+      <c r="DF176" s="0"/>
+      <c r="DG176" s="0"/>
+      <c r="DH176" s="0" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="DI176" s="0"/>
+      <c r="DJ176" s="0"/>
+      <c r="DK176" s="0" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="DL176" s="0"/>
+      <c r="DM176" s="0"/>
+      <c r="DN176" s="0"/>
+      <c r="DO176" s="0" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="DP176" s="0"/>
+      <c r="DQ176" s="0" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="DR176" s="0"/>
+      <c r="DS176" s="0"/>
+      <c r="DT176" s="0"/>
+      <c r="DU176" s="0" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="DV176" s="0"/>
+      <c r="DW176" s="0"/>
+      <c r="DX176" s="0"/>
+      <c r="DY176" s="0"/>
+      <c r="DZ176" s="0"/>
+      <c r="EA176" s="0"/>
+      <c r="EB176" s="0"/>
+      <c r="EC176" s="0"/>
+      <c r="ED176" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="EE176" s="0"/>
+      <c r="EF176" s="0"/>
+      <c r="EG176" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="177">
+      <c r="A177" s="0" t="n">
+        <v>237</v>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E177" s="0" t="n">
+        <v>1324137206</v>
+      </c>
+      <c r="F177" s="0" t="inlineStr">
+        <is>
+          <t>3–5</t>
+        </is>
+      </c>
+      <c r="G177" s="0"/>
+      <c r="H177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="N177" s="0"/>
+      <c r="O177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P177" s="0"/>
+      <c r="Q177" s="0"/>
+      <c r="R177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="S177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T177" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U177" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W177" s="0"/>
+      <c r="X177" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="Y177" s="0"/>
+      <c r="Z177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB177" s="0"/>
+      <c r="AC177" s="0"/>
+      <c r="AD177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE177" s="0"/>
+      <c r="AF177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN177" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO177" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP177" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV177" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW177" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC177" s="0"/>
+      <c r="BD177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE177" s="0"/>
+      <c r="BF177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG177" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ177" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="BK177" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL177" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO177" s="0"/>
+      <c r="BP177" s="0"/>
+      <c r="BQ177" s="0" t="n">
+        <v>966.36</v>
+      </c>
+      <c r="BR177" s="0"/>
+      <c r="BS177" s="0"/>
+      <c r="BT177" s="0" t="n">
+        <v>229.81</v>
+      </c>
+      <c r="BU177" s="0"/>
+      <c r="BV177" s="0" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="BW177" s="0"/>
+      <c r="BX177" s="0"/>
+      <c r="BY177" s="0"/>
+      <c r="BZ177" s="0"/>
+      <c r="CA177" s="0"/>
+      <c r="CB177" s="0" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="CC177" s="0"/>
+      <c r="CD177" s="0"/>
+      <c r="CE177" s="0"/>
+      <c r="CF177" s="0" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="CG177" s="0"/>
+      <c r="CH177" s="0" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="CI177" s="0"/>
+      <c r="CJ177" s="0"/>
+      <c r="CK177" s="0"/>
+      <c r="CL177" s="0"/>
+      <c r="CM177" s="0"/>
+      <c r="CN177" s="0" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="CO177" s="0"/>
+      <c r="CP177" s="0"/>
+      <c r="CQ177" s="0"/>
+      <c r="CR177" s="0"/>
+      <c r="CS177" s="0" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="CT177" s="0"/>
+      <c r="CU177" s="0"/>
+      <c r="CV177" s="0" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="CW177" s="0"/>
+      <c r="CX177" s="0" t="n">
+        <v>73.67</v>
+      </c>
+      <c r="CY177" s="0"/>
+      <c r="CZ177" s="0"/>
+      <c r="DA177" s="0" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="DB177" s="0"/>
+      <c r="DC177" s="0" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="DD177" s="0"/>
+      <c r="DE177" s="0"/>
+      <c r="DF177" s="0"/>
+      <c r="DG177" s="0"/>
+      <c r="DH177" s="0" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="DI177" s="0"/>
+      <c r="DJ177" s="0"/>
+      <c r="DK177" s="0" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="DL177" s="0"/>
+      <c r="DM177" s="0"/>
+      <c r="DN177" s="0"/>
+      <c r="DO177" s="0" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="DP177" s="0"/>
+      <c r="DQ177" s="0" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="DR177" s="0"/>
+      <c r="DS177" s="0"/>
+      <c r="DT177" s="0"/>
+      <c r="DU177" s="0" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="DV177" s="0"/>
+      <c r="DW177" s="0"/>
+      <c r="DX177" s="0"/>
+      <c r="DY177" s="0"/>
+      <c r="DZ177" s="0"/>
+      <c r="EA177" s="0"/>
+      <c r="EB177" s="0"/>
+      <c r="EC177" s="0"/>
+      <c r="ED177" s="0" t="n">
+        <v>142.17</v>
+      </c>
+      <c r="EE177" s="0"/>
+      <c r="EF177" s="0"/>
+      <c r="EG177" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="178">
+      <c r="A178" s="0" t="n">
+        <v>238</v>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E178" s="0" t="n">
+        <v>861572847</v>
+      </c>
+      <c r="F178" s="0" t="inlineStr">
+        <is>
+          <t>3–5</t>
+        </is>
+      </c>
+      <c r="G178" s="0"/>
+      <c r="H178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N178" s="0"/>
+      <c r="O178" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P178" s="0"/>
+      <c r="Q178" s="0"/>
+      <c r="R178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X178" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y178" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB178" s="0"/>
+      <c r="AC178" s="0"/>
+      <c r="AD178" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE178" s="0"/>
+      <c r="AF178" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ178" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL178" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC178" s="0"/>
+      <c r="BD178" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE178" s="0"/>
+      <c r="BF178" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI178" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK178" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM178" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN178" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO178" s="0"/>
+      <c r="BP178" s="0"/>
+      <c r="BQ178" s="0" t="n">
+        <v>627.3</v>
+      </c>
+      <c r="BR178" s="0"/>
+      <c r="BS178" s="0"/>
+      <c r="BT178" s="0" t="n">
+        <v>194.85</v>
+      </c>
+      <c r="BU178" s="0"/>
+      <c r="BV178" s="0" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="BW178" s="0"/>
+      <c r="BX178" s="0"/>
+      <c r="BY178" s="0"/>
+      <c r="BZ178" s="0"/>
+      <c r="CA178" s="0"/>
+      <c r="CB178" s="0" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="CC178" s="0"/>
+      <c r="CD178" s="0"/>
+      <c r="CE178" s="0"/>
+      <c r="CF178" s="0" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="CG178" s="0"/>
+      <c r="CH178" s="0" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="CI178" s="0"/>
+      <c r="CJ178" s="0"/>
+      <c r="CK178" s="0"/>
+      <c r="CL178" s="0"/>
+      <c r="CM178" s="0"/>
+      <c r="CN178" s="0" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="CO178" s="0"/>
+      <c r="CP178" s="0"/>
+      <c r="CQ178" s="0"/>
+      <c r="CR178" s="0"/>
+      <c r="CS178" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="CT178" s="0"/>
+      <c r="CU178" s="0"/>
+      <c r="CV178" s="0" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="CW178" s="0"/>
+      <c r="CX178" s="0" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="CY178" s="0"/>
+      <c r="CZ178" s="0"/>
+      <c r="DA178" s="0" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="DB178" s="0"/>
+      <c r="DC178" s="0" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="DD178" s="0"/>
+      <c r="DE178" s="0"/>
+      <c r="DF178" s="0"/>
+      <c r="DG178" s="0"/>
+      <c r="DH178" s="0" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="DI178" s="0"/>
+      <c r="DJ178" s="0"/>
+      <c r="DK178" s="0" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="DL178" s="0"/>
+      <c r="DM178" s="0"/>
+      <c r="DN178" s="0"/>
+      <c r="DO178" s="0" t="n">
+        <v>8.28</v>
+      </c>
+      <c r="DP178" s="0"/>
+      <c r="DQ178" s="0" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="DR178" s="0"/>
+      <c r="DS178" s="0"/>
+      <c r="DT178" s="0"/>
+      <c r="DU178" s="0" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="DV178" s="0"/>
+      <c r="DW178" s="0"/>
+      <c r="DX178" s="0"/>
+      <c r="DY178" s="0"/>
+      <c r="DZ178" s="0"/>
+      <c r="EA178" s="0"/>
+      <c r="EB178" s="0"/>
+      <c r="EC178" s="0"/>
+      <c r="ED178" s="0" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="EE178" s="0"/>
+      <c r="EF178" s="0"/>
+      <c r="EG178" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="179">
+      <c r="A179" s="0" t="n">
+        <v>239</v>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E179" s="0" t="n">
+        <v>1654066418</v>
+      </c>
+      <c r="F179" s="0" t="inlineStr">
+        <is>
+          <t>10–15</t>
+        </is>
+      </c>
+      <c r="G179" s="0"/>
+      <c r="H179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="L179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M179" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N179" s="0"/>
+      <c r="O179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P179" s="0"/>
+      <c r="Q179" s="0"/>
+      <c r="R179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X179" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB179" s="0"/>
+      <c r="AC179" s="0"/>
+      <c r="AD179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE179" s="0"/>
+      <c r="AF179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK179" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL179" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA179" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC179" s="0"/>
+      <c r="BD179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE179" s="0"/>
+      <c r="BF179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG179" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI179" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK179" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL179" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM179" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO179" s="0"/>
+      <c r="BP179" s="0"/>
+      <c r="BQ179" s="0" t="n">
+        <v>769.18</v>
+      </c>
+      <c r="BR179" s="0"/>
+      <c r="BS179" s="0"/>
+      <c r="BT179" s="0" t="n">
+        <v>385.76</v>
+      </c>
+      <c r="BU179" s="0"/>
+      <c r="BV179" s="0" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="BW179" s="0"/>
+      <c r="BX179" s="0"/>
+      <c r="BY179" s="0"/>
+      <c r="BZ179" s="0"/>
+      <c r="CA179" s="0"/>
+      <c r="CB179" s="0" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="CC179" s="0"/>
+      <c r="CD179" s="0"/>
+      <c r="CE179" s="0"/>
+      <c r="CF179" s="0" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="CG179" s="0"/>
+      <c r="CH179" s="0" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="CI179" s="0"/>
+      <c r="CJ179" s="0"/>
+      <c r="CK179" s="0"/>
+      <c r="CL179" s="0"/>
+      <c r="CM179" s="0"/>
+      <c r="CN179" s="0" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="CO179" s="0"/>
+      <c r="CP179" s="0"/>
+      <c r="CQ179" s="0"/>
+      <c r="CR179" s="0"/>
+      <c r="CS179" s="0" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="CT179" s="0"/>
+      <c r="CU179" s="0"/>
+      <c r="CV179" s="0" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="CW179" s="0"/>
+      <c r="CX179" s="0" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="CY179" s="0"/>
+      <c r="CZ179" s="0"/>
+      <c r="DA179" s="0" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="DB179" s="0"/>
+      <c r="DC179" s="0" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="DD179" s="0"/>
+      <c r="DE179" s="0"/>
+      <c r="DF179" s="0"/>
+      <c r="DG179" s="0"/>
+      <c r="DH179" s="0" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="DI179" s="0"/>
+      <c r="DJ179" s="0"/>
+      <c r="DK179" s="0" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="DL179" s="0"/>
+      <c r="DM179" s="0"/>
+      <c r="DN179" s="0"/>
+      <c r="DO179" s="0" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="DP179" s="0"/>
+      <c r="DQ179" s="0" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="DR179" s="0"/>
+      <c r="DS179" s="0"/>
+      <c r="DT179" s="0"/>
+      <c r="DU179" s="0" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="DV179" s="0"/>
+      <c r="DW179" s="0"/>
+      <c r="DX179" s="0"/>
+      <c r="DY179" s="0"/>
+      <c r="DZ179" s="0"/>
+      <c r="EA179" s="0"/>
+      <c r="EB179" s="0"/>
+      <c r="EC179" s="0"/>
+      <c r="ED179" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="EE179" s="0"/>
+      <c r="EF179" s="0"/>
+      <c r="EG179" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="180">
+      <c r="A180" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E180" s="0" t="n">
+        <v>1334352471</v>
+      </c>
+      <c r="F180" s="0" t="inlineStr">
+        <is>
+          <t>10–15</t>
+        </is>
+      </c>
+      <c r="G180" s="0"/>
+      <c r="H180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M180" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="N180" s="0"/>
+      <c r="O180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="P180" s="0"/>
+      <c r="Q180" s="0"/>
+      <c r="R180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="S180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W180" s="0"/>
+      <c r="X180" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y180" s="0"/>
+      <c r="Z180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB180" s="0"/>
+      <c r="AC180" s="0"/>
+      <c r="AD180" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE180" s="0"/>
+      <c r="AF180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA180" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC180" s="0"/>
+      <c r="BD180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE180" s="0"/>
+      <c r="BF180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH180" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK180" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM180" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO180" s="0"/>
+      <c r="BP180" s="0"/>
+      <c r="BQ180" s="0" t="n">
+        <v>1099.22</v>
+      </c>
+      <c r="BR180" s="0"/>
+      <c r="BS180" s="0"/>
+      <c r="BT180" s="0" t="n">
+        <v>207.71</v>
+      </c>
+      <c r="BU180" s="0"/>
+      <c r="BV180" s="0" t="n">
+        <v>109.22</v>
+      </c>
+      <c r="BW180" s="0"/>
+      <c r="BX180" s="0"/>
+      <c r="BY180" s="0"/>
+      <c r="BZ180" s="0"/>
+      <c r="CA180" s="0"/>
+      <c r="CB180" s="0" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="CC180" s="0"/>
+      <c r="CD180" s="0"/>
+      <c r="CE180" s="0"/>
+      <c r="CF180" s="0" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="CG180" s="0"/>
+      <c r="CH180" s="0" t="n">
+        <v>71.43</v>
+      </c>
+      <c r="CI180" s="0"/>
+      <c r="CJ180" s="0"/>
+      <c r="CK180" s="0"/>
+      <c r="CL180" s="0"/>
+      <c r="CM180" s="0"/>
+      <c r="CN180" s="0" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="CO180" s="0"/>
+      <c r="CP180" s="0"/>
+      <c r="CQ180" s="0"/>
+      <c r="CR180" s="0"/>
+      <c r="CS180" s="0" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="CT180" s="0"/>
+      <c r="CU180" s="0"/>
+      <c r="CV180" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="CW180" s="0"/>
+      <c r="CX180" s="0" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="CY180" s="0"/>
+      <c r="CZ180" s="0"/>
+      <c r="DA180" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="DB180" s="0"/>
+      <c r="DC180" s="0" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="DD180" s="0"/>
+      <c r="DE180" s="0"/>
+      <c r="DF180" s="0"/>
+      <c r="DG180" s="0"/>
+      <c r="DH180" s="0" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="DI180" s="0"/>
+      <c r="DJ180" s="0"/>
+      <c r="DK180" s="0" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="DL180" s="0"/>
+      <c r="DM180" s="0"/>
+      <c r="DN180" s="0"/>
+      <c r="DO180" s="0" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="DP180" s="0"/>
+      <c r="DQ180" s="0" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="DR180" s="0"/>
+      <c r="DS180" s="0"/>
+      <c r="DT180" s="0"/>
+      <c r="DU180" s="0" t="n">
+        <v>84.55</v>
+      </c>
+      <c r="DV180" s="0"/>
+      <c r="DW180" s="0"/>
+      <c r="DX180" s="0"/>
+      <c r="DY180" s="0"/>
+      <c r="DZ180" s="0"/>
+      <c r="EA180" s="0"/>
+      <c r="EB180" s="0"/>
+      <c r="EC180" s="0"/>
+      <c r="ED180" s="0" t="n">
+        <v>98.21</v>
+      </c>
+      <c r="EE180" s="0"/>
+      <c r="EF180" s="0"/>
+      <c r="EG180" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="181">
+      <c r="A181" s="0" t="n">
+        <v>241</v>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C181" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E181" s="0" t="n">
+        <v>1234679120</v>
+      </c>
+      <c r="F181" s="0" t="inlineStr">
+        <is>
+          <t>3–5</t>
+        </is>
+      </c>
+      <c r="G181" s="0"/>
+      <c r="H181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="N181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="O181" s="0"/>
+      <c r="P181" s="0"/>
+      <c r="Q181" s="0"/>
+      <c r="R181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="T181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W181" s="0"/>
+      <c r="X181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB181" s="0"/>
+      <c r="AC181" s="0"/>
+      <c r="AD181" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="AE181" s="0"/>
+      <c r="AF181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC181" s="0"/>
+      <c r="BD181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF181" s="0"/>
+      <c r="BG181" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI181" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ181" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK181" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL181" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM181" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN181" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO181" s="0"/>
+      <c r="BP181" s="0"/>
+      <c r="BQ181" s="0" t="n">
+        <v>735.69</v>
+      </c>
+      <c r="BR181" s="0"/>
+      <c r="BS181" s="0"/>
+      <c r="BT181" s="0" t="n">
+        <v>204.48</v>
+      </c>
+      <c r="BU181" s="0"/>
+      <c r="BV181" s="0" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="BW181" s="0"/>
+      <c r="BX181" s="0"/>
+      <c r="BY181" s="0"/>
+      <c r="BZ181" s="0"/>
+      <c r="CA181" s="0"/>
+      <c r="CB181" s="0" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="CC181" s="0"/>
+      <c r="CD181" s="0"/>
+      <c r="CE181" s="0"/>
+      <c r="CF181" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="CG181" s="0"/>
+      <c r="CH181" s="0" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="CI181" s="0"/>
+      <c r="CJ181" s="0"/>
+      <c r="CK181" s="0"/>
+      <c r="CL181" s="0"/>
+      <c r="CM181" s="0"/>
+      <c r="CN181" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="CO181" s="0"/>
+      <c r="CP181" s="0"/>
+      <c r="CQ181" s="0"/>
+      <c r="CR181" s="0"/>
+      <c r="CS181" s="0" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="CT181" s="0"/>
+      <c r="CU181" s="0"/>
+      <c r="CV181" s="0" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="CW181" s="0"/>
+      <c r="CX181" s="0" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="CY181" s="0"/>
+      <c r="CZ181" s="0"/>
+      <c r="DA181" s="0" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="DB181" s="0"/>
+      <c r="DC181" s="0" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="DD181" s="0"/>
+      <c r="DE181" s="0"/>
+      <c r="DF181" s="0"/>
+      <c r="DG181" s="0"/>
+      <c r="DH181" s="0" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="DI181" s="0"/>
+      <c r="DJ181" s="0"/>
+      <c r="DK181" s="0" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="DL181" s="0"/>
+      <c r="DM181" s="0"/>
+      <c r="DN181" s="0"/>
+      <c r="DO181" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="DP181" s="0"/>
+      <c r="DQ181" s="0" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="DR181" s="0"/>
+      <c r="DS181" s="0"/>
+      <c r="DT181" s="0"/>
+      <c r="DU181" s="0" t="n">
+        <v>47.76</v>
+      </c>
+      <c r="DV181" s="0"/>
+      <c r="DW181" s="0"/>
+      <c r="DX181" s="0"/>
+      <c r="DY181" s="0"/>
+      <c r="DZ181" s="0"/>
+      <c r="EA181" s="0"/>
+      <c r="EB181" s="0"/>
+      <c r="EC181" s="0"/>
+      <c r="ED181" s="0" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="EE181" s="0"/>
+      <c r="EF181" s="0"/>
+      <c r="EG181" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="182">
+      <c r="A182" s="0" t="n">
+        <v>242</v>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C182" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E182" s="0" t="n">
+        <v>790113216</v>
+      </c>
+      <c r="F182" s="0" t="inlineStr">
+        <is>
+          <t>3–5</t>
+        </is>
+      </c>
+      <c r="G182" s="0"/>
+      <c r="H182" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="N182" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="O182" s="0"/>
+      <c r="P182" s="0"/>
+      <c r="Q182" s="0"/>
+      <c r="R182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V182" s="0"/>
+      <c r="W182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="X182" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y182" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB182" s="0"/>
+      <c r="AC182" s="0"/>
+      <c r="AD182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE182" s="0"/>
+      <c r="AF182" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL182" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA182" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC182" s="0"/>
+      <c r="BD182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE182" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF182" s="0"/>
+      <c r="BG182" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI182" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK182" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL182" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM182" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN182" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO182" s="0"/>
+      <c r="BP182" s="0"/>
+      <c r="BQ182" s="0" t="n">
+        <v>557.54</v>
+      </c>
+      <c r="BR182" s="0"/>
+      <c r="BS182" s="0"/>
+      <c r="BT182" s="0" t="n">
+        <v>204.82</v>
+      </c>
+      <c r="BU182" s="0"/>
+      <c r="BV182" s="0" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BW182" s="0"/>
+      <c r="BX182" s="0"/>
+      <c r="BY182" s="0"/>
+      <c r="BZ182" s="0"/>
+      <c r="CA182" s="0"/>
+      <c r="CB182" s="0" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="CC182" s="0"/>
+      <c r="CD182" s="0"/>
+      <c r="CE182" s="0"/>
+      <c r="CF182" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="CG182" s="0"/>
+      <c r="CH182" s="0" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="CI182" s="0"/>
+      <c r="CJ182" s="0"/>
+      <c r="CK182" s="0"/>
+      <c r="CL182" s="0"/>
+      <c r="CM182" s="0"/>
+      <c r="CN182" s="0" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="CO182" s="0"/>
+      <c r="CP182" s="0"/>
+      <c r="CQ182" s="0"/>
+      <c r="CR182" s="0"/>
+      <c r="CS182" s="0" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="CT182" s="0"/>
+      <c r="CU182" s="0"/>
+      <c r="CV182" s="0" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="CW182" s="0"/>
+      <c r="CX182" s="0" t="n">
+        <v>9.21</v>
+      </c>
+      <c r="CY182" s="0"/>
+      <c r="CZ182" s="0"/>
+      <c r="DA182" s="0" t="n">
+        <v>8.37</v>
+      </c>
+      <c r="DB182" s="0"/>
+      <c r="DC182" s="0" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="DD182" s="0"/>
+      <c r="DE182" s="0"/>
+      <c r="DF182" s="0"/>
+      <c r="DG182" s="0"/>
+      <c r="DH182" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="DI182" s="0"/>
+      <c r="DJ182" s="0"/>
+      <c r="DK182" s="0" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="DL182" s="0"/>
+      <c r="DM182" s="0"/>
+      <c r="DN182" s="0"/>
+      <c r="DO182" s="0" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="DP182" s="0"/>
+      <c r="DQ182" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="DR182" s="0"/>
+      <c r="DS182" s="0"/>
+      <c r="DT182" s="0"/>
+      <c r="DU182" s="0" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="DV182" s="0"/>
+      <c r="DW182" s="0"/>
+      <c r="DX182" s="0"/>
+      <c r="DY182" s="0"/>
+      <c r="DZ182" s="0"/>
+      <c r="EA182" s="0"/>
+      <c r="EB182" s="0"/>
+      <c r="EC182" s="0"/>
+      <c r="ED182" s="0" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="EE182" s="0"/>
+      <c r="EF182" s="0"/>
+      <c r="EG182" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="183">
+      <c r="A183" s="0" t="n">
+        <v>243</v>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E183" s="0" t="n">
+        <v>842143307</v>
+      </c>
+      <c r="F183" s="0" t="inlineStr">
+        <is>
+          <t>3–5</t>
+        </is>
+      </c>
+      <c r="G183" s="0"/>
+      <c r="H183" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M183" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="O183" s="0"/>
+      <c r="P183" s="0"/>
+      <c r="Q183" s="0"/>
+      <c r="R183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="W183" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="X183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB183" s="0"/>
+      <c r="AC183" s="0"/>
+      <c r="AD183" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE183" s="0"/>
+      <c r="AF183" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG183" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL183" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA183" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC183" s="0"/>
+      <c r="BD183" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF183" s="0"/>
+      <c r="BG183" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH183" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI183" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ183" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK183" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM183" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN183" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO183" s="0"/>
+      <c r="BP183" s="0"/>
+      <c r="BQ183" s="0" t="n">
+        <v>1761.24</v>
+      </c>
+      <c r="BR183" s="0"/>
+      <c r="BS183" s="0"/>
+      <c r="BT183" s="0" t="n">
+        <v>488</v>
+      </c>
+      <c r="BU183" s="0"/>
+      <c r="BV183" s="0" t="n">
+        <v>131.71</v>
+      </c>
+      <c r="BW183" s="0"/>
+      <c r="BX183" s="0"/>
+      <c r="BY183" s="0"/>
+      <c r="BZ183" s="0"/>
+      <c r="CA183" s="0"/>
+      <c r="CB183" s="0" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="CC183" s="0"/>
+      <c r="CD183" s="0"/>
+      <c r="CE183" s="0"/>
+      <c r="CF183" s="0" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="CG183" s="0"/>
+      <c r="CH183" s="0" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="CI183" s="0"/>
+      <c r="CJ183" s="0"/>
+      <c r="CK183" s="0"/>
+      <c r="CL183" s="0"/>
+      <c r="CM183" s="0"/>
+      <c r="CN183" s="0" t="n">
+        <v>137.98</v>
+      </c>
+      <c r="CO183" s="0"/>
+      <c r="CP183" s="0"/>
+      <c r="CQ183" s="0"/>
+      <c r="CR183" s="0"/>
+      <c r="CS183" s="0" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="CT183" s="0"/>
+      <c r="CU183" s="0"/>
+      <c r="CV183" s="0" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="CW183" s="0"/>
+      <c r="CX183" s="0" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="CY183" s="0"/>
+      <c r="CZ183" s="0"/>
+      <c r="DA183" s="0" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="DB183" s="0"/>
+      <c r="DC183" s="0" t="n">
+        <v>75.71</v>
+      </c>
+      <c r="DD183" s="0"/>
+      <c r="DE183" s="0"/>
+      <c r="DF183" s="0"/>
+      <c r="DG183" s="0"/>
+      <c r="DH183" s="0" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="DI183" s="0"/>
+      <c r="DJ183" s="0"/>
+      <c r="DK183" s="0" t="n">
+        <v>152.81</v>
+      </c>
+      <c r="DL183" s="0"/>
+      <c r="DM183" s="0"/>
+      <c r="DN183" s="0"/>
+      <c r="DO183" s="0" t="n">
+        <v>64.71</v>
+      </c>
+      <c r="DP183" s="0"/>
+      <c r="DQ183" s="0" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="DR183" s="0"/>
+      <c r="DS183" s="0"/>
+      <c r="DT183" s="0"/>
+      <c r="DU183" s="0" t="n">
+        <v>189.59</v>
+      </c>
+      <c r="DV183" s="0"/>
+      <c r="DW183" s="0"/>
+      <c r="DX183" s="0"/>
+      <c r="DY183" s="0"/>
+      <c r="DZ183" s="0"/>
+      <c r="EA183" s="0"/>
+      <c r="EB183" s="0"/>
+      <c r="EC183" s="0"/>
+      <c r="ED183" s="0" t="n">
+        <v>78.4</v>
+      </c>
+      <c r="EE183" s="0"/>
+      <c r="EF183" s="0"/>
+      <c r="EG183" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="184">
+      <c r="A184" s="0" t="n">
+        <v>245</v>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D184" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E184" s="0" t="n">
+        <v>1825578171</v>
+      </c>
+      <c r="F184" s="0" t="inlineStr">
+        <is>
+          <t>10–15</t>
+        </is>
+      </c>
+      <c r="G184" s="0"/>
+      <c r="H184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="L184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="M184" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N184" s="0"/>
+      <c r="O184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P184" s="0"/>
+      <c r="Q184" s="0"/>
+      <c r="R184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB184" s="0"/>
+      <c r="AC184" s="0"/>
+      <c r="AD184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE184" s="0"/>
+      <c r="AF184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK184" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL184" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR184" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS184" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT184" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY184" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ184" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA184" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB184" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC184" s="0"/>
+      <c r="BD184" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE184" s="0"/>
+      <c r="BF184" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG184" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI184" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ184" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK184" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM184" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN184" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO184" s="0"/>
+      <c r="BP184" s="0"/>
+      <c r="BQ184" s="0" t="n">
+        <v>978.08</v>
+      </c>
+      <c r="BR184" s="0"/>
+      <c r="BS184" s="0"/>
+      <c r="BT184" s="0" t="n">
+        <v>201.13</v>
+      </c>
+      <c r="BU184" s="0"/>
+      <c r="BV184" s="0" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="BW184" s="0"/>
+      <c r="BX184" s="0"/>
+      <c r="BY184" s="0"/>
+      <c r="BZ184" s="0"/>
+      <c r="CA184" s="0"/>
+      <c r="CB184" s="0" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="CC184" s="0"/>
+      <c r="CD184" s="0"/>
+      <c r="CE184" s="0"/>
+      <c r="CF184" s="0" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="CG184" s="0"/>
+      <c r="CH184" s="0" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="CI184" s="0"/>
+      <c r="CJ184" s="0"/>
+      <c r="CK184" s="0"/>
+      <c r="CL184" s="0"/>
+      <c r="CM184" s="0"/>
+      <c r="CN184" s="0" t="n">
+        <v>72.43</v>
+      </c>
+      <c r="CO184" s="0"/>
+      <c r="CP184" s="0"/>
+      <c r="CQ184" s="0"/>
+      <c r="CR184" s="0"/>
+      <c r="CS184" s="0" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="CT184" s="0"/>
+      <c r="CU184" s="0"/>
+      <c r="CV184" s="0" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="CW184" s="0"/>
+      <c r="CX184" s="0" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="CY184" s="0"/>
+      <c r="CZ184" s="0"/>
+      <c r="DA184" s="0" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="DB184" s="0"/>
+      <c r="DC184" s="0" t="n">
+        <v>108.82</v>
+      </c>
+      <c r="DD184" s="0"/>
+      <c r="DE184" s="0"/>
+      <c r="DF184" s="0"/>
+      <c r="DG184" s="0"/>
+      <c r="DH184" s="0" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="DI184" s="0"/>
+      <c r="DJ184" s="0"/>
+      <c r="DK184" s="0" t="n">
+        <v>96.45</v>
+      </c>
+      <c r="DL184" s="0"/>
+      <c r="DM184" s="0"/>
+      <c r="DN184" s="0"/>
+      <c r="DO184" s="0" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="DP184" s="0"/>
+      <c r="DQ184" s="0" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="DR184" s="0"/>
+      <c r="DS184" s="0"/>
+      <c r="DT184" s="0"/>
+      <c r="DU184" s="0" t="n">
+        <v>68.59</v>
+      </c>
+      <c r="DV184" s="0"/>
+      <c r="DW184" s="0"/>
+      <c r="DX184" s="0"/>
+      <c r="DY184" s="0"/>
+      <c r="DZ184" s="0"/>
+      <c r="EA184" s="0"/>
+      <c r="EB184" s="0"/>
+      <c r="EC184" s="0"/>
+      <c r="ED184" s="0" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="EE184" s="0"/>
+      <c r="EF184" s="0"/>
+      <c r="EG184" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="185">
+      <c r="A185" s="0" t="n">
+        <v>246</v>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E185" s="0" t="n">
+        <v>43731212</v>
+      </c>
+      <c r="F185" s="0" t="inlineStr">
+        <is>
+          <t>3–5</t>
+        </is>
+      </c>
+      <c r="G185" s="0"/>
+      <c r="H185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="O185" s="0"/>
+      <c r="P185" s="0"/>
+      <c r="Q185" s="0"/>
+      <c r="R185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="W185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="X185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB185" s="0"/>
+      <c r="AC185" s="0"/>
+      <c r="AD185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE185" s="0"/>
+      <c r="AF185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB185" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC185" s="0"/>
+      <c r="BD185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF185" s="0"/>
+      <c r="BG185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH185" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK185" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL185" s="0" t="n">
+        <v>99</v>
+      </c>
+      <c r="BM185" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN185" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO185" s="0"/>
+      <c r="BP185" s="0"/>
+      <c r="BQ185" s="0" t="n">
+        <v>829.56</v>
+      </c>
+      <c r="BR185" s="0"/>
+      <c r="BS185" s="0"/>
+      <c r="BT185" s="0" t="n">
+        <v>268.55</v>
+      </c>
+      <c r="BU185" s="0"/>
+      <c r="BV185" s="0" t="n">
+        <v>159.28</v>
+      </c>
+      <c r="BW185" s="0"/>
+      <c r="BX185" s="0"/>
+      <c r="BY185" s="0"/>
+      <c r="BZ185" s="0"/>
+      <c r="CA185" s="0"/>
+      <c r="CB185" s="0" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="CC185" s="0"/>
+      <c r="CD185" s="0"/>
+      <c r="CE185" s="0"/>
+      <c r="CF185" s="0" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="CG185" s="0"/>
+      <c r="CH185" s="0" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="CI185" s="0"/>
+      <c r="CJ185" s="0"/>
+      <c r="CK185" s="0"/>
+      <c r="CL185" s="0"/>
+      <c r="CM185" s="0"/>
+      <c r="CN185" s="0" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="CO185" s="0"/>
+      <c r="CP185" s="0"/>
+      <c r="CQ185" s="0"/>
+      <c r="CR185" s="0"/>
+      <c r="CS185" s="0" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="CT185" s="0"/>
+      <c r="CU185" s="0"/>
+      <c r="CV185" s="0" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="CW185" s="0"/>
+      <c r="CX185" s="0" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="CY185" s="0"/>
+      <c r="CZ185" s="0"/>
+      <c r="DA185" s="0" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="DB185" s="0"/>
+      <c r="DC185" s="0" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="DD185" s="0"/>
+      <c r="DE185" s="0"/>
+      <c r="DF185" s="0"/>
+      <c r="DG185" s="0"/>
+      <c r="DH185" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="DI185" s="0"/>
+      <c r="DJ185" s="0"/>
+      <c r="DK185" s="0" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="DL185" s="0"/>
+      <c r="DM185" s="0"/>
+      <c r="DN185" s="0"/>
+      <c r="DO185" s="0" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="DP185" s="0"/>
+      <c r="DQ185" s="0" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="DR185" s="0"/>
+      <c r="DS185" s="0"/>
+      <c r="DT185" s="0"/>
+      <c r="DU185" s="0" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="DV185" s="0"/>
+      <c r="DW185" s="0"/>
+      <c r="DX185" s="0"/>
+      <c r="DY185" s="0"/>
+      <c r="DZ185" s="0"/>
+      <c r="EA185" s="0"/>
+      <c r="EB185" s="0"/>
+      <c r="EC185" s="0"/>
+      <c r="ED185" s="0" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="EE185" s="0"/>
+      <c r="EF185" s="0"/>
+      <c r="EG185" s="0"/>
+    </row>
+    <row collapsed="false" customFormat="false" customHeight="false" hidden="false" ht="12.1" outlineLevel="0" r="186">
+      <c r="A186" s="0" t="n">
+        <v>247</v>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t>1980-01-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D186" s="0" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E186" s="0" t="n">
+        <v>718327804</v>
+      </c>
+      <c r="F186" s="0" t="inlineStr">
+        <is>
+          <t>20–30</t>
+        </is>
+      </c>
+      <c r="G186" s="0"/>
+      <c r="H186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="L186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="M186" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N186" s="0"/>
+      <c r="O186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="P186" s="0"/>
+      <c r="Q186" s="0"/>
+      <c r="R186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="U186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="W186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="X186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB186" s="0"/>
+      <c r="AC186" s="0"/>
+      <c r="AD186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE186" s="0"/>
+      <c r="AF186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC186" s="0"/>
+      <c r="BD186" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE186" s="0"/>
+      <c r="BF186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI186" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ186" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK186" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL186" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO186" s="0"/>
+      <c r="BP186" s="0"/>
+      <c r="BQ186" s="0" t="n">
+        <v>895.6</v>
+      </c>
+      <c r="BR186" s="0"/>
+      <c r="BS186" s="0"/>
+      <c r="BT186" s="0" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="BU186" s="0"/>
+      <c r="BV186" s="0" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="BW186" s="0"/>
+      <c r="BX186" s="0"/>
+      <c r="BY186" s="0"/>
+      <c r="BZ186" s="0"/>
+      <c r="CA186" s="0"/>
+      <c r="CB186" s="0" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="CC186" s="0"/>
+      <c r="CD186" s="0"/>
+      <c r="CE186" s="0"/>
+      <c r="CF186" s="0" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="CG186" s="0"/>
+      <c r="CH186" s="0" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="CI186" s="0"/>
+      <c r="CJ186" s="0"/>
+      <c r="CK186" s="0"/>
+      <c r="CL186" s="0"/>
+      <c r="CM186" s="0"/>
+      <c r="CN186" s="0" t="n">
+        <v>79.27</v>
+      </c>
+      <c r="CO186" s="0"/>
+      <c r="CP186" s="0"/>
+      <c r="CQ186" s="0"/>
+      <c r="CR186" s="0"/>
+      <c r="CS186" s="0" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="CT186" s="0"/>
+      <c r="CU186" s="0"/>
+      <c r="CV186" s="0" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="CW186" s="0"/>
+      <c r="CX186" s="0" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="CY186" s="0"/>
+      <c r="CZ186" s="0"/>
+      <c r="DA186" s="0" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="DB186" s="0"/>
+      <c r="DC186" s="0" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="DD186" s="0"/>
+      <c r="DE186" s="0"/>
+      <c r="DF186" s="0"/>
+      <c r="DG186" s="0"/>
+      <c r="DH186" s="0" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="DI186" s="0"/>
+      <c r="DJ186" s="0"/>
+      <c r="DK186" s="0" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="DL186" s="0"/>
+      <c r="DM186" s="0"/>
+      <c r="DN186" s="0"/>
+      <c r="DO186" s="0" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="DP186" s="0"/>
+      <c r="DQ186" s="0" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="DR186" s="0"/>
+      <c r="DS186" s="0"/>
+      <c r="DT186" s="0"/>
+      <c r="DU186" s="0" t="n">
+        <v>141</v>
+      </c>
+      <c r="DV186" s="0"/>
+      <c r="DW186" s="0"/>
+      <c r="DX186" s="0"/>
+      <c r="DY186" s="0"/>
+      <c r="DZ186" s="0"/>
+      <c r="EA186" s="0"/>
+      <c r="EB186" s="0"/>
+      <c r="EC186" s="0"/>
+      <c r="ED186" s="0" t="n">
+        <v>37.19</v>
+      </c>
+      <c r="EE186" s="0"/>
+      <c r="EF186" s="0"/>
+      <c r="EG186" s="0"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
